--- a/微博测试链接1.xlsx
+++ b/微博测试链接1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="125">
   <si>
     <t>序号</t>
   </si>
@@ -53,31 +53,401 @@
     <t>摘要</t>
   </si>
   <si>
-    <t xml:space="preserve">	-</t>
-  </si>
-  <si>
-    <t>深圳陈红</t>
+    <t>点赞数</t>
+  </si>
+  <si>
+    <t>评论数</t>
+  </si>
+  <si>
+    <t>分享数</t>
+  </si>
+  <si>
+    <t>播放/浏览数</t>
+  </si>
+  <si>
+    <t>链接有效性</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>泰兰尼斯“送礼”广告争议背后：千元标价与38元出厂底</t>
+  </si>
+  <si>
+    <t>新黄河大鱼财经</t>
+  </si>
+  <si>
+    <t>新浪长微博</t>
+  </si>
+  <si>
+    <t>2026-05-14 13:57:30</t>
+  </si>
+  <si>
+    <t>疑似敏感</t>
+  </si>
+  <si>
+    <t>https://weibo.com/ttarticle/p/show?id=2309405298474609672388</t>
+  </si>
+  <si>
+    <t>近日，一则“工作上承蒙您照顾，宝宝小脚我来照顾”的广告引发争议，也让外界重新算起了泰兰尼斯童鞋逼近2000元的高价账。
+新黄河记者调查发现，在铺天盖地的电梯广告和千元标价背后，招商人员给出了“门店利润最高可达70%”的承诺。而与之形成强烈反差的，是官方处罚文书中低至37.8元的出厂成本，以及长达五年间同类安全问题多次重演的抽检不合格记录。
+**一则“送礼”广告，将这个高价童鞋品牌再次推上台前**
+在这则引发争议的广告画面中，一名女职员将一张泰兰尼斯鞋卡递给了被称为“王姐”的女上司，并配以“工作上承蒙您照顾，宝宝小脚我来照顾”的台词。这段将童鞋与职场人情直接绑定的视频，迅速在社交平台上引发...</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>无效</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>仿大牌衣服货源哪里批发市场?市场热门商品推荐</t>
+  </si>
+  <si>
+    <t>xiangfeng211_462</t>
+  </si>
+  <si>
+    <t>2026-05-14 13:55:51</t>
+  </si>
+  <si>
+    <t>正面</t>
+  </si>
+  <si>
+    <t>https://weibo.com/ttarticle/p/show?id=2309405298474194436121</t>
+  </si>
+  <si>
+    <t>仿大牌衣服货源哪里批发市场?市场热门商品推荐
+![](https://wx2.sinaimg.cn/large/a21566b8ly1id4ygmwmosj20k00k0wgg.jpg)
+仿大牌衣服货源批发市场及热门商品推荐
+近年来，仿大牌衣服以其高性价比、时尚设计和追随潮流的特点吸引了越来越多的消费者。无论是年轻的时尚达人还是经济实惠的普通消费者，仿大牌衣服都是一个不错的选择。那么，仿大牌衣服的货源通常来自哪些批发市场呢？在这里，我们将探讨几个主要的批发市场，并推荐一些市场热门商品及价格层级。
+1\. 主要批发市场
+广州服装批发市场
+广州被誉为中国的“时尚之都”，其服装批发市场如...</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>安提瓜护照移民得花多少钱</t>
+  </si>
+  <si>
+    <t>洲际移民老王</t>
+  </si>
+  <si>
+    <t>2026-05-14 13:53:16</t>
+  </si>
+  <si>
+    <t>https://weibo.com/ttarticle/p/show?id=2309405298473544581142</t>
+  </si>
+  <si>
+    <t>打算通过投资入籍拿一本安提瓜护照的朋友，最关心的问题之一就是费用。网上信息零零碎碎，今天就把安提瓜护照移民的价格构成一项项说清楚，包括捐款和购房两种方式的具体开销，以及不同家庭规模下到底要准备多少预算。
+![图片](https://wx2.sinaimg.cn/large/008HKHXkgy1id4ydak5zkj30m80dw0wu.jpg)
+### 一、安提瓜护照的两种主流投资方式
+安提瓜和巴布达在2013年将投资入籍计划写入《投资入籍法》，主要接受两类投资路径：向国家发展基金捐款，或者购买政府批准的房产。
+**1.1 捐款方式**
+捐款方式操作简单，资金直接进入安提瓜国家发展...</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>樱雪地暖（YINGXUE）官 方| 24h中央人工服务售后</t>
+  </si>
+  <si>
+    <t>鱿小鱿小I鱿小鱼</t>
+  </si>
+  <si>
+    <t>2026-05-14 13:51:03</t>
+  </si>
+  <si>
+    <t>https://weibo.com/ttarticle/p/show?id=2309405298472986476658</t>
+  </si>
+  <si>
+    <t>??40000;6, 6,089（2026全新推出）  
+全年值守快速响应，舒心体验，一键开启——品质卓越，用起来特别放心，没有任何安全隐患，让人安心使用。  
+?? ??樱雪地暖（YINGXUE）：400--006-6
+-089，一键呼叫，服务到家——樱雪地暖（YINGXUE）400,00,6.60;89顺潮流之向，创非凡之业。主动关怀产品使用场景，定期推荐适配配件与耗材，拓展产品实用价值。我们深知您的樱雪地暖（YINGXUE）电器对您意义非凡，因此我们提供全方位的，让您的樱雪地暖（YINGXUE）在使用中随时享受如家的呵护：  
+  ...</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>高仿男包哪里有,均在这10个地点！</t>
+  </si>
+  <si>
+    <t>伊莎微购服装商行</t>
+  </si>
+  <si>
+    <t>2026-05-14 13:45:42</t>
+  </si>
+  <si>
+    <t>https://weibo.com/ttarticle/p/show?id=2309405298471640105004</t>
+  </si>
+  <si>
+    <t>高仿男包哪里有,均在这10个地点！  
+![](https://wx2.sinaimg.cn/large/005H8h3hly1id4y68vc3kj30j60j6jui.jpg)
+高仿男包哪里有,均在这10个地点！  
+在当今快节奏的现代生活中，男包不仅是实用工具，也是彰显个人品味的重要配饰。对于那些追求时尚但又预算有限的朋友来说，高仿男包是一个不错的选择。那么，高仿男包哪里有呢？本文为您揭晓10个购买高仿男包的地点，并提供详细的价格参考和购买渠道建议，帮助您轻松找到心仪的产品。  
+一、广州白云皮具城  
+广州白云皮具城是国内最知名的高仿男包批发市场之一。这里汇集了众多品...</t>
+  </si>
+  <si>
+    <t>487</t>
+  </si>
+  <si>
+    <t>国宝对话 | 平陆运河与科技革命</t>
+  </si>
+  <si>
+    <t>宽窄有度</t>
+  </si>
+  <si>
+    <t>2026-05-14 13:40:00</t>
+  </si>
+  <si>
+    <t>https://weibo.com/ttarticle/p/show?id=2309405298470214041767</t>
+  </si>
+  <si>
+    <t>![](https://wx2.sinaimg.cn/large/006CpPojly4id3x7j3kxej30u0179n1b.jpg)
+**宽窄说**
+ **窄开新脉，宽联八方；**
+**河通江海，业兴西南。**
+**基建筑基，科技领航；**
+**水织宏图，国启新章。**
+​
+共计3750字，大约需要7.5分钟
+​
+截止到2026年5月初，平陆运河整体进度已达95%，27座跨运河桥梁已全部完工，这条运河历经4年建设，将于9月试运行，年底正式通航。
+​
+2021年9月，我去广西做调研，一位当地领导的秘书向我讲述了平陆运河对广西的重要性，以及浙赣粤大运...</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>感谢很甜的羽的微博视频</t>
+  </si>
+  <si>
+    <t>感谢很甜的羽</t>
+  </si>
+  <si>
+    <t>新浪微博视频</t>
+  </si>
+  <si>
+    <t>2026-05-14 14:01:47</t>
+  </si>
+  <si>
+    <t>https://weibo.com/tv/show/1034:5298475685052520</t>
+  </si>
+  <si>
+    <t>#李歪歪[超话]# 我们有这么臭吗[哼][哼]歪歪!回答我!哼?,感谢很甜的羽的微博视频,感谢很甜的羽,新浪微博视频,浙江省杭州市</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>杭州发布的微博视频</t>
+  </si>
+  <si>
+    <t>杭州发布</t>
+  </si>
+  <si>
+    <t>2026-05-14 14:00:05</t>
+  </si>
+  <si>
+    <t>https://weibo.com/tv/show/1034:5298475257233475</t>
+  </si>
+  <si>
+    <t>【真正的“神兵天降”！#出租车侧翻杭州特警用警车搭桥救人#】#杭州特警脚踏警车救出被困的哥# 5月12日中午，杭州环城北路一辆出租车因司机分心撞上水马侧翻，横停路中引发拥堵，司机被困车内。特警PTU火速赶到，“00后”特警张博渊发现司机意识清醒但被卡住。他急中生智，指挥同事将警车,杭州发布的微博视频,杭州发布,新浪微博视频,浙江省</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>浙江少儿频道的微博视频</t>
+  </si>
+  <si>
+    <t>浙江少儿频道</t>
+  </si>
+  <si>
+    <t>2026-05-14 13:57:14</t>
+  </si>
+  <si>
+    <t>https://weibo.com/tv/show/1034:5298474539745284</t>
+  </si>
+  <si>
+    <t>外卖小哥心脏骤停倒地，路过的护士不顾膝盖受伤跪地救人。成功唤醒外卖小哥意识。外卖小哥送医后已无大碍。（来源：杭州发布） #杭州护士街头跪地救回倒地小哥##正能量##暖心瞬间#,浙江少儿频道的微博视频,浙江少儿频道,外卖小哥心脏骤停倒地 路过的护士不顾膝盖疼痛跪地救人 外卖小哥成功恢复意识 5月13日浙江杭州 路人 好心人微博视频号 儿辅边 外卖小哥心脏骤停倒地 路过的护士不顾膝盖疼痛跪地救人 外卖小哥成功恢复意识 5月13日浙江杭州 路人 北大街这里 （120通话）外卖小哥心脏骤停倒地 路过的护士不顾膝盖疼痛跪地救人 外卖小哥成功恢复意识 5月13日浙江杭州P 微博视频号 浙江少儿道 外卖小哥...</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>家长带孩子在马路中间骑玩具车，路过司机纷纷鸣笛提醒。</t>
+  </si>
+  <si>
+    <t>蓝色的烟卷</t>
+  </si>
+  <si>
+    <t>2026-05-14 13:51:35</t>
+  </si>
+  <si>
+    <t>https://weibo.com/tv/show/1034:5298473118138454</t>
+  </si>
+  <si>
+    <t>近日，杭州。家长带孩子在马路中间骑玩具车，路过司机纷纷鸣笛提醒。,家长带孩子在马路中间骑玩具车，路过司机纷纷鸣笛提醒。,蓝色的烟卷,新浪微博视频,湖南省</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>#网易严选全球代言人梓渝#🔮#520向梓渝告白# ...</t>
+  </si>
+  <si>
+    <t>小小蘑菇渝011</t>
   </si>
   <si>
     <t>新浪微博</t>
   </si>
   <si>
-    <t>2026-05-08 12:26:45</t>
+    <t>2026-05-14 14:07:43</t>
+  </si>
+  <si>
+    <t>https://weibo.com/8212373973/QFjQ9EhMo</t>
+  </si>
+  <si>
+    <t>#网易严选全球代言人梓渝#🔮#520向梓渝告白# .
+YUNI用爱意托举商业大盘，纯粉购买力创造销售奇迹，梓渝值得最好的排面与最耀眼的成绩单！梓渝粉丝YUNI
+@我是梓渝_ ​,小小蘑菇渝011,网易严选 15” × 首都爱护动物协会 CAPITALANIMALWELFAREASSOCIATION 十年相伴更懂彼此 毛茸茸守护计划 梓渝 动物保护公益大使 网易严选全球代言人 研 景 全价鲜蒸犬粮 lA1  全价鲜蒸猫粮 r23 | RETLSHE务网易严选网易严选115 ? 微博视频号 @网易严选梓渝商务观察系列一一业内妈粉写给梓渝的成长笔记 福 POST 购买认准 @月之必要 梓渝的商...</t>
+  </si>
+  <si>
+    <t>有效</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>早上打车走高速，起太早太困了在车上睡着了，司机付了...</t>
+  </si>
+  <si>
+    <t>当我是死的麼</t>
+  </si>
+  <si>
+    <t>2026-05-14 14:07:36</t>
   </si>
   <si>
     <t>负面</t>
   </si>
   <si>
-    <t>https://weibo.com/5721059494/QEoCccOGT</t>
-  </si>
-  <si>
-    <t>真的看得人心惊又心寒！
-谁都想不到一场惨烈事故，
-拖垮整个浏阳烟花行业！浏阳这家开了二十多年的烟花厂。
-谁能想到，出事这家并不是三无小作坊。
-整整800亩场地，在浏阳做烟花足足26年，妥妥老牌大厂。
-按道理这么多年经验，什么危险不懂，偏偏抱着侥幸乱来。浏阳市华盛烟花制造燃放有限公司发生爆炸事故。截止到5月8日12时，事故造成37人死亡
-#浏阳烟花厂爆炸已致37死##财经#,深圳陈红,新浪微博,其他</t>
+    <t>https://weibo.com/3025387092/QFjQ6FSDf</t>
+  </si>
+  <si>
+    <t>早上打车走高速，起太早太困了在车上睡着了，司机付了过路费，没给我发票，报销不了啊啊啊！一趟非必要行程我还要往里贴钱，精力财力的双重损失，真的气死我了啊啊啊！,当我是死的麼,新浪微博,香港特别行政区北区</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>蘑菇渝1号</t>
+  </si>
+  <si>
+    <t>2026-05-14 14:07:27</t>
+  </si>
+  <si>
+    <t>https://weibo.com/5458398014/QFjQ37a3K</t>
+  </si>
+  <si>
+    <t>#网易严选全球代言人梓渝#🔮#520向梓渝告白# .
+ 🐾 梓渝粉丝YUNI一起追随梓渝，把这份温柔的爱传递给更多毛孩子！支持全球代言人梓渝，守护流浪小动物，让美好心愿落地生根。
+@我是梓渝_ ​,蘑菇渝1号,YU-LU-WEHLIANG 小红书 ? @深海胖头渝务S @我是梓渝@miktaratesutet tartlesute!官宣战报 官宣战报 24小时 24小时 证 梓渝 网易严送全珠代言 邪 1o.0706 No.0706 24小时全品类销售额 24小时全品类销售额 道包含网易严送天猫/京车/丹高/APP 课道包含网易严选抖音/天猫/原东/APP 3240W+ 小红书 331...</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>蘑菇鱼5号</t>
+  </si>
+  <si>
+    <t>2026-05-14 14:07:17</t>
+  </si>
+  <si>
+    <t>https://weibo.com/7969788665/QFjPZb6v7</t>
+  </si>
+  <si>
+    <t>#网易严选全球代言人梓渝#🔮#520向梓渝告白# .
+官宣20分钟登顶星品影响力TOP1，梓渝的商业号召力断层领先，YUNI永远是你最坚实的后盾！梓渝粉丝YUNI
+@我是梓渝_ ​,蘑菇鱼5号,S @我是梓渝微博 CELEBRITY COMMERCIALVALUE 星品影响力 本周NO.1 星品影响力指数 @网易严选 1.07 @我是梓渝_ 网易严选 亿 数据周期：05.04-05.10 na新浪娱乐 微博娱乐 微博娱乐商业 微博搜索 星品影响力 O @星品影响力网易严选115 @网易严选梓渝 Haru_Selene梓渝商务观察系列一一业内妈粉写给梓渝的成长笔记 福 POST 购买认准 ...</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>养只喵名为渝</t>
+  </si>
+  <si>
+    <t>2026-05-14 14:07:12</t>
+  </si>
+  <si>
+    <t>https://weibo.com/9112489784/QFjPWBZrk</t>
+  </si>
+  <si>
+    <t>#网易严选全球代言人梓渝#🔮#520向梓渝告白# .
+微博开屏即见梓渝，YUNI每天打开手机都是惊喜！梓渝的国民度太高，YUNI的排面必须安排！
+@我是梓渝_ ​,养只喵名为渝,网易严选110 D 微博视频号 电 @网易严 号 YU-LU-WEHLIANG 小红书 ? @深海胖头渝务网易严选 15” 给你柔软的梦境 和醒来的好心情 梓渝 网易严选全球代言人 G证 网易严选小蓝棒深睡枕 还原颈椎自然曲线承托每晚好眠 @网易严选网易严选梓渝商务观察系列一一业内妈粉写给梓渝的成长笔记 福 POST 购买认准 @月之必要 梓渝的商务 布局系列文 网易严选续约梓渝为全球代言人，双方携手推动宠 物业...</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>杭州的物价真是惊人 这一份沙县小吃鸡腿饭居然要17...</t>
+  </si>
+  <si>
+    <t>阿媚Erin</t>
+  </si>
+  <si>
+    <t>2026-05-14 14:07:09</t>
+  </si>
+  <si>
+    <t>https://weibo.com/6144678425/QFjPVkzHe</t>
+  </si>
+  <si>
+    <t>杭州的物价真是惊人 这一份沙县小吃鸡腿饭居然要17块 印象中不是13块的吗[泪奔] ​,阿媚Erin,新浪微博,其他</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>#社工发现楼梯拐角有血救回独居老人#</t>
+  </si>
+  <si>
+    <t>今日诸城</t>
+  </si>
+  <si>
+    <t>2026-05-14 14:07:07</t>
+  </si>
+  <si>
+    <t>https://weibo.com/1249548545/QFjPUrjSg</t>
+  </si>
+  <si>
+    <t>【#社工发现楼梯拐角有血救回独居老人#】5月14日（发布），据杭州日报，前阵子的一个下午，杭州朝晖街道华联社区的社工李莉在日常巡查时，发现小区某单元楼梯口，竟然出现了一小摊新鲜血迹。
+这位社工平时就负责老小区的日常巡查。这天，她原本是检查下楼道的卫生情况。这一摊血面积并不大，甚至可以说，不太起眼。“就那么一小摊，还有几滴，都没干涸，就在楼梯口转角的位置。老实说，要不是检查卫生，我还真不一定会发现。”李莉说，“在社区工作这几年，从来没见过楼道里有血，所以一下子就警觉起来。”
+她接下来看到的情况，更让她感到紧张。因为抬头往楼梯上看，沿着楼梯血迹断断续续都有出现。李莉顺着血迹，一层楼一层楼往上走...</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>蘑菇小鱼10号</t>
+  </si>
+  <si>
+    <t>https://weibo.com/3725750773/QFjPV2WXq</t>
+  </si>
+  <si>
+    <t>#网易严选全球代言人梓渝#🔮#520向梓渝告白# .
+居家日用与个护香氛全线登顶，梓渝的全品类带货能力太强，YUNI的钱包永远为你准备着！梓渝粉丝YUNI
+@我是梓渝_ ​,蘑菇小鱼10号,网易严选110 D 微博视频号 电 @网易严 号 +s41c务官宣战报 官宣战报 24小时 24小时 证 梓渝 网易严送全珠代言 邪 1o.0706 No.0706 24小时全品类销售额 24小时全品类销售额 道包含网易严送天猫/京车/丹高/APP 课道包含网易严选抖音/天猫/原东/APP 3240W+ 小红书 3310W+ 894191梓渝 Haru_Selene网易严选 官宣战报 24小时  茶 ...</t>
   </si>
 </sst>
 </file>
@@ -734,7 +1104,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -747,8 +1117,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1275,10 +1648,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1" outlineLevelRow="1" outlineLevelCol="7"/>
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1"/>
+  <cols>
+    <col min="4" max="4" width="21.1531531531532" customWidth="1"/>
+    <col min="7" max="7" width="48.6486486486486" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1303,36 +1680,767 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:8">
-      <c r="A2" s="3">
+    <row r="2" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A16" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A17" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A18" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>3875</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
+      <c r="A19" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="https://weibo.com/5721059494/QEoCccOGT" tooltip="https://weibo.com/5721059494/QEoCccOGT"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://weibo.com/ttarticle/p/show?id=2309405298474609672388"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://weibo.com/ttarticle/p/show?id=2309405298474194436121"/>
+    <hyperlink ref="G8" r:id="rId3" display="https://weibo.com/tv/show/1034:5298475685052520"/>
+    <hyperlink ref="G18" r:id="rId4" display="https://weibo.com/1249548545/QFjPUrjSg"/>
+    <hyperlink ref="G15" r:id="rId5" display="https://weibo.com/7969788665/QFjPZb6v7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
